--- a/output/pdf_financials_xlsx/STCK.xlsx
+++ b/output/pdf_financials_xlsx/STCK.xlsx
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>7.538624</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -5884,7 +5884,11 @@
           <t>Warrant reserve 6</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>7.538624</v>
       </c>

--- a/output/pdf_financials_xlsx/STCK.xlsx
+++ b/output/pdf_financials_xlsx/STCK.xlsx
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.222931</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.826491</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.371461</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.814337</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.5772699999999999</v>
+        <v>-0.8002010000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.848708</v>
+        <v>-1.675199</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.218998</v>
+        <v>-5.590459</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15.992163</v>
+        <v>15.177826</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1113,16 +1113,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.5772699999999999</v>
+        <v>-0.8002010000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.848708</v>
+        <v>-1.675199</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.218998</v>
+        <v>-5.590459</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15.992163</v>
+        <v>15.177826</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>76.338241</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>29.891193</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>25.074005</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>11.259678</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>17.260946</v>
       </c>
     </row>
     <row r="35">
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>76.338241</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>29.891193</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>25.074005</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>11.259678</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>17.260946</v>
       </c>
     </row>
     <row r="37">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E260" s="5" t="n">

--- a/output/pdf_financials_xlsx/STCK.xlsx
+++ b/output/pdf_financials_xlsx/STCK.xlsx
@@ -3196,16 +3196,16 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.47757</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-1.312743</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.417796</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-1.608834</v>
       </c>
     </row>
     <row r="122">
@@ -6598,7 +6598,11 @@
           <t>Share repurchase $</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -7121,7 +7125,11 @@
           <t>Share repurchase $</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -7488,7 +7496,11 @@
           <t>Share-based compensation expense 6</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -7607,7 +7619,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -8097,7 +8113,11 @@
           <t>Share repurchase 5</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -8179,7 +8199,11 @@
           <t>Proceeds from management private placement 5</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
         <v>7.000008</v>
       </c>
@@ -8759,7 +8783,11 @@
           <t>Proceeds from management private placement 5, 7</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>7.000008</v>
       </c>
